--- a/data/trans_orig/IP31KM10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM10_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65458</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55119</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75301</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42122</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34113</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51232</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70700</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57652</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82373</t>
+          <t>50981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>112823</t>
+          <t>108034</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97759</t>
+          <t>95982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128360</t>
+          <t>121027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55751</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45908</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>59587</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50477</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67596</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>58,59%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64476</t>
+          <t>57773</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>49368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77524</t>
+          <t>66111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>124063</t>
+          <t>113524</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108526</t>
+          <t>100531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139127</t>
+          <t>125576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>56,68%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51890</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42967</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60279</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>67,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>46448</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37961</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53995</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>49,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53022</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>40299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>57781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>99470</t>
+          <t>100462</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87925</t>
+          <t>89684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112134</t>
+          <t>112940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37990</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46913</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46944</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39397</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55431</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>37629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>87631</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74967</t>
+          <t>72350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99176</t>
+          <t>95606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33754</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27338</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39497</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25249</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19579</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31933</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>60872</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22090</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28506</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18156</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>49,59%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26710</t>
+          <t>25330</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>32741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>51550</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>36507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60894</t>
+          <t>55395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>125678</t>
+          <t>105775</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106255</t>
+          <t>92757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159278</t>
+          <t>121397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>112467</t>
+          <t>93152</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97834</t>
+          <t>82433</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127748</t>
+          <t>104257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>238145</t>
+          <t>198928</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213323</t>
+          <t>182324</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272216</t>
+          <t>217169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91538</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75916</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>104556</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>89859</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>56259</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>109282</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>83488</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84910</t>
+          <t>72383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114824</t>
+          <t>94207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>190051</t>
+          <t>175025</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155980</t>
+          <t>156784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214873</t>
+          <t>191629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>93060</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>82036</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>105426</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>59525</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50156</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>69209</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>51,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>60301</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87009</t>
+          <t>51253</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115715</t>
+          <t>68857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>160254</t>
+          <t>153361</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144528</t>
+          <t>138466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178051</t>
+          <t>168528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>52526</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40160</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>63550</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>55984</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46300</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>65353</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58732</t>
+          <t>55165</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>46609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72452</t>
+          <t>64213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>114716</t>
+          <t>107691</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96919</t>
+          <t>92524</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>122586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44159</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>36504</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>50513</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>67,05%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>55,42%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>76,69%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>39731</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>32447</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>46873</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>57,67%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>47,1%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>68,04%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>83985</t>
+          <t>85881</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73707</t>
+          <t>75418</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94142</t>
+          <t>95883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21704</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15350</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>29359</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>32,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>44,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>29164</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22022</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>36448</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>42,33%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>31,96%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>52,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24777</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>37295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>50339</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43783</t>
+          <t>40337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64218</t>
+          <t>60802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>394096</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>367419</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>415659</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>54,38%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>61,52%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>338751</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>312245</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>381492</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>59,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>416796</t>
+          <t>313003</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>388301</t>
+          <t>291406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>444266</t>
+          <t>333591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>755548</t>
+          <t>707100</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>715309</t>
+          <t>675845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>807334</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>281599</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>260036</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>308276</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>41,68%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>45,62%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>306380</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>263639</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>332886</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>40,87%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>315572</t>
+          <t>297229</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288102</t>
+          <t>276641</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344067</t>
+          <t>318826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>621951</t>
+          <t>578827</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570165</t>
+          <t>545860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662190</t>
+          <t>610082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
